--- a/data/trans_orig/P6711-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6711-Clase-trans_orig.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2012</t>
+          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14242</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31882</t>
+          <t>32450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>42059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40156</t>
+          <t>39529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65812</t>
+          <t>67345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25957</t>
+          <t>27943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21403</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>20827</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43348</t>
+          <t>42848</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44606</t>
+          <t>44939</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74686</t>
+          <t>72455</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>17614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37829</t>
+          <t>38177</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69147</t>
+          <t>68214</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103582</t>
+          <t>102870</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29732</t>
+          <t>29378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51835</t>
+          <t>53044</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>37999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>53030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83822</t>
+          <t>83452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147957</t>
+          <t>145634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>182661</t>
+          <t>180717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81784</t>
+          <t>82220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110641</t>
+          <t>110943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>236909</t>
+          <t>237508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>282592</t>
+          <t>283433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,25%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>24131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>17226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36218</t>
+          <t>37536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>29418</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56680</t>
+          <t>55203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>27816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>14305</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13893</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35445</t>
+          <t>32851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44617</t>
+          <t>45252</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74239</t>
+          <t>74703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16199</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35785</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64645</t>
+          <t>66345</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103014</t>
+          <t>102155</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44507</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71496</t>
+          <t>71813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>27939</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50791</t>
+          <t>51638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78030</t>
+          <t>78366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114693</t>
+          <t>114803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90751</t>
+          <t>90506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124183</t>
+          <t>125102</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60584</t>
+          <t>59971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87576</t>
+          <t>86788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158711</t>
+          <t>160445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203493</t>
+          <t>203378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40069</t>
+          <t>39384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>21903</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43831</t>
+          <t>43093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>22584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>27403</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51742</t>
+          <t>50996</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22633</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39139</t>
+          <t>37503</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66194</t>
+          <t>65434</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36419</t>
+          <t>36763</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62010</t>
+          <t>61230</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26192</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51493</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81536</t>
+          <t>82571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140058</t>
+          <t>139344</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173982</t>
+          <t>175135</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62225</t>
+          <t>62282</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82268</t>
+          <t>82486</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>209338</t>
+          <t>209469</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>249896</t>
+          <t>249332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52620</t>
+          <t>51788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83788</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34761</t>
+          <t>35191</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59341</t>
+          <t>61362</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95444</t>
+          <t>93038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135047</t>
+          <t>133926</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>24566</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49614</t>
+          <t>49653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>16743</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37248</t>
+          <t>37437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47720</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79238</t>
+          <t>79814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69855</t>
+          <t>68559</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>103196</t>
+          <t>102219</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45087</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72605</t>
+          <t>74703</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>121439</t>
+          <t>122272</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>166839</t>
+          <t>165827</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60290</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90631</t>
+          <t>93127</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44406</t>
+          <t>45342</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71216</t>
+          <t>72809</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113758</t>
+          <t>112812</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154429</t>
+          <t>154868</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143515</t>
+          <t>144221</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>183611</t>
+          <t>184561</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95269</t>
+          <t>93660</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>127830</t>
+          <t>128202</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246038</t>
+          <t>250266</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>300232</t>
+          <t>303950</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17925</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37885</t>
+          <t>36598</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37308</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39965</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>68181</t>
+          <t>68600</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36235</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42942</t>
+          <t>43741</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36681</t>
+          <t>35933</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>25897</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31851</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>56243</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31313</t>
+          <t>30784</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53848</t>
+          <t>53905</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>29021</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52124</t>
+          <t>51655</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>65300</t>
+          <t>66268</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>97043</t>
+          <t>97054</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>41035</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>64990</t>
+          <t>66190</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>55796</t>
+          <t>54933</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>83765</t>
+          <t>81872</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>104939</t>
+          <t>105451</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>140811</t>
+          <t>141437</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4131,107 +4131,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159106</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134363</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184469</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130995</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111018</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153924</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290101</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258775</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>323970</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -4244,107 +4244,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85180</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68569</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104647</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72949</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57123</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91915</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>146</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158129</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135989</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184591</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -4357,107 +4357,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>247</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265481</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237444</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>297501</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139432</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119944</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163678</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>377</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>404913</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367005</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441440</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -4470,107 +4470,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>262402</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>232702</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290776</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>169</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179957</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156259</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206109</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>424</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>442358</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403035</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481335</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -4583,107 +4583,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>645792</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>607701</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683056</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>389</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>421957</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>391257</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>457061</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1067748</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1017357</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1118798</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -4696,804 +4696,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1417961</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1417961</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1417961</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>873</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>945290</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>945290</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>945290</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2363250</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2363250</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2363250</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>159106</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>135140</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>187696</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>130995</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>109113</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>151900</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>16,07%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>290101</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>261031</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>324660</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>85180</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>67807</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>104222</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>72949</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>57302</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>92366</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>158129</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>135331</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>183177</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>265481</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>237508</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>297677</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>139432</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>117339</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>163264</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>12,41%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>404913</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>369878</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>444998</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>262402</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>234572</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>293311</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>18,51%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>179957</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>157693</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>208098</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>16,68%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>22,01%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>442358</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>405761</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>481282</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>645792</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>609132</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>687135</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>45,54%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>42,96%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>48,46%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>421957</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>388759</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>456692</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>44,64%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>41,13%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>48,31%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1067748</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>1017359</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1120068</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>45,18%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>43,05%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>47,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1331</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1417961</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1417961</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1417961</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>873</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>945290</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>945290</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>945290</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2204</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2363250</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2363250</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2363250</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>
@@ -5513,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5544,7 +4861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2016</t>
+          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5739,12 +5056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46811</t>
+          <t>45877</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5754,12 +5071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5774,12 +5091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30264</t>
+          <t>29895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53995</t>
+          <t>55377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5789,12 +5106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5809,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>57307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91162</t>
+          <t>90739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5824,12 +5141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36298</t>
+          <t>36922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23260</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44838</t>
+          <t>43494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5902,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43079</t>
+          <t>43744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75014</t>
+          <t>73425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39775</t>
+          <t>40013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68011</t>
+          <t>66457</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28296</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51455</t>
+          <t>51399</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74177</t>
+          <t>75533</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110912</t>
+          <t>109832</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57516</t>
+          <t>56840</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>86966</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28674</t>
+          <t>27921</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50609</t>
+          <t>50449</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91801</t>
+          <t>91668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131644</t>
+          <t>130127</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79502</t>
+          <t>81163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113855</t>
+          <t>113443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51091</t>
+          <t>50558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77421</t>
+          <t>77670</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138722</t>
+          <t>138903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183123</t>
+          <t>181230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31815</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56053</t>
+          <t>55253</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45591</t>
+          <t>45921</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6471,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61215</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93902</t>
+          <t>93977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6506,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>20475</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>42492</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>18143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>37489</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42903</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72445</t>
+          <t>72541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42229</t>
+          <t>43781</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68968</t>
+          <t>70479</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52646</t>
+          <t>53996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81300</t>
+          <t>81099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115486</t>
+          <t>116118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39253</t>
+          <t>38036</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64454</t>
+          <t>64102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>27200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50522</t>
+          <t>50132</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73291</t>
+          <t>73623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107048</t>
+          <t>106688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50710</t>
+          <t>50760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78984</t>
+          <t>79129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36099</t>
+          <t>36471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60911</t>
+          <t>61874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93994</t>
+          <t>93955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133367</t>
+          <t>131448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29604</t>
+          <t>29797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7138,12 +6455,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7153,12 +6470,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36162</t>
+          <t>34643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7188,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24106</t>
+          <t>24372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7251,12 +6568,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7266,12 +6583,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14445</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>31843</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38097</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62960</t>
+          <t>62542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43124</t>
+          <t>43890</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71543</t>
+          <t>71730</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49068</t>
+          <t>48109</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76778</t>
+          <t>76128</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>26690</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64147</t>
+          <t>64576</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95835</t>
+          <t>94979</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59128</t>
+          <t>58466</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87737</t>
+          <t>85702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39360</t>
+          <t>38836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85954</t>
+          <t>85460</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>120441</t>
+          <t>119142</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56603</t>
+          <t>58212</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90298</t>
+          <t>90417</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7820,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66921</t>
+          <t>66006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97322</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7835,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>131245</t>
+          <t>131953</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179091</t>
+          <t>175655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64493</t>
+          <t>63898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98463</t>
+          <t>97532</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>44856</t>
+          <t>44876</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>71508</t>
+          <t>70470</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7953,7 +7270,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>113839</t>
+          <t>116547</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>158431</t>
+          <t>159661</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104746</t>
+          <t>104010</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>142152</t>
+          <t>143808</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77385</t>
+          <t>75063</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>110769</t>
+          <t>109803</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>191834</t>
+          <t>191951</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>243079</t>
+          <t>243303</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88744</t>
+          <t>89383</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125966</t>
+          <t>126465</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81620</t>
+          <t>78716</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>150529</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197096</t>
+          <t>196510</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89073</t>
+          <t>89036</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126092</t>
+          <t>126215</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57846</t>
+          <t>58856</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>88844</t>
+          <t>88620</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>157045</t>
+          <t>155602</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>203256</t>
+          <t>203152</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>29393</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54047</t>
+          <t>54301</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>24656</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>46443</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62349</t>
+          <t>60231</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>95694</t>
+          <t>93679</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43819</t>
+          <t>43561</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31964</t>
+          <t>31751</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42316</t>
+          <t>41899</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71095</t>
+          <t>69411</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30156</t>
+          <t>30501</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>53981</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>42964</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>68192</t>
+          <t>68069</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>80082</t>
+          <t>80503</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>114782</t>
+          <t>115614</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>21362</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43416</t>
+          <t>42268</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34732</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>58456</t>
+          <t>60048</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>62718</t>
+          <t>62016</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>94083</t>
+          <t>94179</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>35821</t>
+          <t>37335</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>60561</t>
+          <t>62362</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28805</t>
+          <t>28753</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51578</t>
+          <t>51052</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8969,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70733</t>
+          <t>71130</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>105416</t>
+          <t>104365</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +8446,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9139,107 +8456,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>190</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208978</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>180100</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>235194</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>194402</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168436</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220562</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>377</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403380</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367449</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441072</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -9252,107 +8569,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>168</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>182394</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156051</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208373</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>142</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143422</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>122581</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166368</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325816</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293997</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>361676</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -9365,107 +8682,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>306</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>322826</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>291182</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353689</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>236464</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208578</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>263513</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>540</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>559290</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>516469</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>603611</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -9478,107 +8795,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>299</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>320729</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>289026</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355224</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207484</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184624</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234674</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>504</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>528213</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>487360</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>573244</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -9591,107 +8908,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>360</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387395</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352818</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>427127</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>254448</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223732</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>281391</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>604</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>641843</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>593438</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>685394</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -9704,804 +9021,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>208978</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>183727</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>242179</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>14,69%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>12,92%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>194402</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>169653</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>217285</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>18,76%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>20,97%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>403380</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>365264</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>440295</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>17,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>182394</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>159464</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>211966</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>143422</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>122013</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>168597</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>325816</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>296582</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>360006</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>322826</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>289795</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>355911</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>22,7%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>25,02%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>236464</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>211470</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>264644</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>22,82%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>20,41%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>559290</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>513727</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>599938</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>20,9%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>320729</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>287616</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>352724</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>22,55%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>24,8%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>207484</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>180822</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>233745</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>22,56%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>528213</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>486701</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>567666</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>19,8%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>23,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>387395</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>352342</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>421121</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>24,77%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>29,61%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>254448</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>227789</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>283161</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>24,56%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>21,98%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>27,33%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>641843</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>595749</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>690141</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>26,11%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>24,23%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>28,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>

--- a/data/trans_orig/P6711-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6711-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32450</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>19963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>41743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39529</t>
+          <t>39146</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67345</t>
+          <t>66890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>27026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>21370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>20617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42848</t>
+          <t>44113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44939</t>
+          <t>44515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72455</t>
+          <t>73989</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>37936</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68214</t>
+          <t>67068</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102870</t>
+          <t>103456</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29378</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53044</t>
+          <t>52276</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>38592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>53485</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83452</t>
+          <t>85599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145634</t>
+          <t>146020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180717</t>
+          <t>182522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82220</t>
+          <t>81603</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110943</t>
+          <t>110672</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237508</t>
+          <t>236834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>283433</t>
+          <t>284306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24131</t>
+          <t>25594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37536</t>
+          <t>36929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29418</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55203</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27816</t>
+          <t>27738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>14237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32851</t>
+          <t>34880</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45252</t>
+          <t>45012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74703</t>
+          <t>75334</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>34906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66345</t>
+          <t>66997</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102155</t>
+          <t>101434</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43289</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71813</t>
+          <t>72386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>27419</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>50633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78366</t>
+          <t>78291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114803</t>
+          <t>114805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90506</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125102</t>
+          <t>124363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59971</t>
+          <t>62053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86788</t>
+          <t>88591</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160445</t>
+          <t>159921</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203378</t>
+          <t>202896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,99%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39384</t>
+          <t>39497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21903</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43093</t>
+          <t>42957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10266</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27403</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50996</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22074</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65434</t>
+          <t>65503</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36763</t>
+          <t>37474</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61230</t>
+          <t>62404</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>11172</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82571</t>
+          <t>82330</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>139344</t>
+          <t>139972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175135</t>
+          <t>175320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62282</t>
+          <t>61754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82486</t>
+          <t>82040</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>209469</t>
+          <t>211504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>249332</t>
+          <t>249261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51788</t>
+          <t>53120</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84366</t>
+          <t>85438</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35191</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61362</t>
+          <t>61116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93038</t>
+          <t>94584</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133926</t>
+          <t>137660</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49653</t>
+          <t>49072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37437</t>
+          <t>37469</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>47205</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79814</t>
+          <t>79089</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>68559</t>
+          <t>68432</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102219</t>
+          <t>102691</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45343</t>
+          <t>45321</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>74703</t>
+          <t>74149</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>122272</t>
+          <t>122235</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>165827</t>
+          <t>165459</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60241</t>
+          <t>59171</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93127</t>
+          <t>91442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45342</t>
+          <t>46063</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72809</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112812</t>
+          <t>112139</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154868</t>
+          <t>154894</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>144221</t>
+          <t>144745</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>184561</t>
+          <t>184596</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>93660</t>
+          <t>94518</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>128202</t>
+          <t>128225</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>250266</t>
+          <t>248501</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>303950</t>
+          <t>299428</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>18298</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36598</t>
+          <t>37747</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>37937</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>68600</t>
+          <t>65710</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>11967</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38341</t>
+          <t>36435</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43741</t>
+          <t>43077</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35933</t>
+          <t>35623</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25897</t>
+          <t>25663</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30442</t>
+          <t>31485</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t>55686</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30784</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53905</t>
+          <t>53030</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>29380</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>51655</t>
+          <t>51363</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>66268</t>
+          <t>66309</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>97054</t>
+          <t>97592</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>41126</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>66190</t>
+          <t>65812</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>54933</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>81872</t>
+          <t>81114</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>105451</t>
+          <t>102145</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>141437</t>
+          <t>139049</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>134363</t>
+          <t>135957</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>184469</t>
+          <t>182864</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>111018</t>
+          <t>109625</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>153924</t>
+          <t>154316</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>258775</t>
+          <t>260373</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>323970</t>
+          <t>323439</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>68569</t>
+          <t>68244</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>104647</t>
+          <t>104676</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>57123</t>
+          <t>58140</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>91915</t>
+          <t>92767</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>135989</t>
+          <t>136483</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>184591</t>
+          <t>184447</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>237444</t>
+          <t>235039</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>297501</t>
+          <t>296152</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>119944</t>
+          <t>119228</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>163678</t>
+          <t>166245</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>367005</t>
+          <t>370370</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>441440</t>
+          <t>447327</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>232702</t>
+          <t>232387</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>290776</t>
+          <t>291982</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>156259</t>
+          <t>159369</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>206109</t>
+          <t>209895</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>403035</t>
+          <t>406902</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>481335</t>
+          <t>482757</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>607701</t>
+          <t>605113</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>683056</t>
+          <t>686304</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>391257</t>
+          <t>391861</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>457061</t>
+          <t>454007</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1017357</t>
+          <t>1016766</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1118798</t>
+          <t>1120371</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,41%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23110</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45877</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29895</t>
+          <t>30417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55377</t>
+          <t>54757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57307</t>
+          <t>55808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90739</t>
+          <t>87758</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>17334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36922</t>
+          <t>37339</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>22153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43494</t>
+          <t>42248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43744</t>
+          <t>42796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73425</t>
+          <t>73205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40013</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66457</t>
+          <t>67308</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29269</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51399</t>
+          <t>51191</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75533</t>
+          <t>75564</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109832</t>
+          <t>112455</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56840</t>
+          <t>56162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86966</t>
+          <t>87688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50449</t>
+          <t>51665</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91668</t>
+          <t>93050</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130127</t>
+          <t>132544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>81634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113443</t>
+          <t>112426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50558</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77670</t>
+          <t>77426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138903</t>
+          <t>137755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181230</t>
+          <t>180263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>32371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55253</t>
+          <t>56588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23858</t>
+          <t>24274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45921</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62155</t>
+          <t>61403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93977</t>
+          <t>96935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42492</t>
+          <t>41897</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>17268</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37489</t>
+          <t>36990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43065</t>
+          <t>43687</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72541</t>
+          <t>72811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43781</t>
+          <t>42760</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70479</t>
+          <t>71565</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31361</t>
+          <t>30252</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53996</t>
+          <t>52478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81099</t>
+          <t>82140</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>116118</t>
+          <t>116944</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>39223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64102</t>
+          <t>64542</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27200</t>
+          <t>29420</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50132</t>
+          <t>52373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73623</t>
+          <t>72507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106688</t>
+          <t>106656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50760</t>
+          <t>49922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79129</t>
+          <t>79933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>37029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61874</t>
+          <t>60345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93955</t>
+          <t>95385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131448</t>
+          <t>132246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15924</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34643</t>
+          <t>35063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24372</t>
+          <t>23213</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38097</t>
+          <t>36946</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62542</t>
+          <t>63037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43890</t>
+          <t>44324</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71730</t>
+          <t>71646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48109</t>
+          <t>47823</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76128</t>
+          <t>76432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26690</t>
+          <t>26180</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64576</t>
+          <t>64584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94979</t>
+          <t>95279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58466</t>
+          <t>58815</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85702</t>
+          <t>87252</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38836</t>
+          <t>38637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85460</t>
+          <t>86698</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119142</t>
+          <t>118550</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58212</t>
+          <t>56777</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90417</t>
+          <t>90380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66006</t>
+          <t>66019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>97322</t>
+          <t>97132</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>131953</t>
+          <t>133792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>175655</t>
+          <t>176588</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>63898</t>
+          <t>64635</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97532</t>
+          <t>96883</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>44876</t>
+          <t>44719</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>70470</t>
+          <t>71197</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>116547</t>
+          <t>115813</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>159661</t>
+          <t>160596</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104010</t>
+          <t>104897</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>143808</t>
+          <t>144176</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>75063</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109803</t>
+          <t>109922</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>191951</t>
+          <t>188865</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>243303</t>
+          <t>241752</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>89383</t>
+          <t>90072</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126465</t>
+          <t>124170</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>52346</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78716</t>
+          <t>80325</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148901</t>
+          <t>150719</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196510</t>
+          <t>195632</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89036</t>
+          <t>88945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126215</t>
+          <t>125655</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58856</t>
+          <t>59752</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>88620</t>
+          <t>89522</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>155602</t>
+          <t>157246</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>203152</t>
+          <t>203397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54301</t>
+          <t>55373</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24656</t>
+          <t>25388</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46443</t>
+          <t>47684</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60231</t>
+          <t>61773</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93679</t>
+          <t>94973</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43561</t>
+          <t>44928</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>32235</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41899</t>
+          <t>41726</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69411</t>
+          <t>69373</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30501</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53981</t>
+          <t>53896</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42964</t>
+          <t>44503</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>68069</t>
+          <t>69469</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>115614</t>
+          <t>113070</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42268</t>
+          <t>43724</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34306</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>60048</t>
+          <t>58971</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>62016</t>
+          <t>62678</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>94179</t>
+          <t>94033</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37335</t>
+          <t>36111</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>62362</t>
+          <t>61353</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28753</t>
+          <t>29948</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51052</t>
+          <t>51457</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>71130</t>
+          <t>71285</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>104365</t>
+          <t>105269</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>180100</t>
+          <t>182424</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>235194</t>
+          <t>235679</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>168436</t>
+          <t>171163</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>220562</t>
+          <t>221010</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>367449</t>
+          <t>367836</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>441072</t>
+          <t>442089</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>156051</t>
+          <t>156323</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>208373</t>
+          <t>209598</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>122581</t>
+          <t>122721</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>166368</t>
+          <t>166227</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>293997</t>
+          <t>291967</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>361676</t>
+          <t>363277</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>291182</t>
+          <t>292172</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>353689</t>
+          <t>359023</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>208578</t>
+          <t>210052</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>263513</t>
+          <t>265135</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>516469</t>
+          <t>522007</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>603611</t>
+          <t>601838</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>289026</t>
+          <t>288436</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>355224</t>
+          <t>354467</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>184624</t>
+          <t>182841</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>234674</t>
+          <t>233151</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>487360</t>
+          <t>486523</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>573244</t>
+          <t>572304</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -8918,12 +8918,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>352818</t>
+          <t>355631</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>427127</t>
+          <t>425663</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>223732</t>
+          <t>229477</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>281391</t>
+          <t>284401</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>593438</t>
+          <t>599301</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>685394</t>
+          <t>688511</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
